--- a/output/pdf_financials_xlsx/GOAT.xlsx
+++ b/output/pdf_financials_xlsx/GOAT.xlsx
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.863875</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.974425</v>
       </c>
     </row>
     <row r="93">
@@ -2606,7 +2606,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>1.863875</v>
       </c>

--- a/output/pdf_financials_xlsx/GOAT.xlsx
+++ b/output/pdf_financials_xlsx/GOAT.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.006623</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000887</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.006623</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000887</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.025109</v>
+        <v>0.018486</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.000887</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
